--- a/src/attributions/attributions_ig_traj_384.xlsx
+++ b/src/attributions/attributions_ig_traj_384.xlsx
@@ -1568,46 +1568,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.04336864930999965</v>
+        <v>0.02421498618992464</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1494473196319425</v>
+        <v>0.03126600021906353</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.08257398871976092</v>
+        <v>-0.02626976608495128</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.112679144607185</v>
+        <v>0.108141222738961</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.02193713557834307</v>
+        <v>-0.00314018867253042</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03652602937493087</v>
+        <v>0.01300682920709993</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -1619,22 +1619,22 @@
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1426540625819782</v>
+        <v>-0.01272444610492863</v>
       </c>
       <c r="T3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0239358898883534</v>
+        <v>0.01572157589450173</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.04684453693333857</v>
+        <v>-0.04301912973122161</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
@@ -1646,136 +1646,136 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.06761159567421682</v>
+        <v>0.02570572557363097</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.02019065258513931</v>
+        <v>-0.03084232238080361</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.08274849248120011</v>
+        <v>-0.01238652320637592</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.016744346770511</v>
+        <v>0.01231553465678581</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.009927665879051032</v>
+        <v>-0.04430130766599427</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1484187386627861</v>
+        <v>-0.07028130971568153</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
         <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.03601114337502941</v>
+        <v>-0.08579843094236166</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.4405310731998979</v>
+        <v>0.008754885749072945</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.24058948594978</v>
+        <v>-0.1649646257099339</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.02964815708051309</v>
+        <v>0.01205035926648909</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.001660136129609598</v>
+        <v>0.002094287017081302</v>
       </c>
       <c r="BF3" t="n">
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-2.070405578483767e-11</v>
+        <v>2.798382843295607e-11</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
         <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.04785674797654764</v>
+        <v>0.04606782634114693</v>
       </c>
       <c r="BM3" t="n">
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.02557243125243977</v>
+        <v>-0.006944643635793998</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.309924960790316</v>
+        <v>0.05481150081527637</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,73 +1784,73 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.00172645647647363</v>
+        <v>-0.07237072223251699</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.2279419119677277</v>
+        <v>0.06080899034809523</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.01543375230698284</v>
+        <v>-0.07600144699273473</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
         <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.08721065091882951</v>
+        <v>0.05479844575663927</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.09776271306189981</v>
+        <v>-0.01597635524953257</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.1408110664165099</v>
+        <v>0.05336674118103343</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
         <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.02952700911101509</v>
+        <v>-0.004705852729613262</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.06562678213649012</v>
+        <v>0.006706560149099621</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.2759720408694346</v>
+        <v>-0.04367625310775392</v>
       </c>
       <c r="CR3" t="n">
         <v>-0</v>
@@ -1859,31 +1859,31 @@
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
         <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.1022703270904006</v>
+        <v>0.04561282647821253</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.07238452113836454</v>
+        <v>-0.02898868808057231</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.1112361507300692</v>
+        <v>0.02065477713867466</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,46 +1892,46 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.05108503375986372</v>
+        <v>0.03158797502303493</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.00203212217615888</v>
+        <v>0.0003107776144800823</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.02522300447708196</v>
+        <v>0.1209867558940659</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.07167939129624269</v>
+        <v>0.04572454235911425</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.08839402274098884</v>
+        <v>0.02067030561046682</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.2504688668656428</v>
+        <v>-0.04811539520837225</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
@@ -1943,49 +1943,49 @@
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.08724125411306345</v>
+        <v>0.01760957140882726</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.009793797064961954</v>
+        <v>0.09255285634787529</v>
       </c>
       <c r="DZ3" t="n">
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.07483299877393977</v>
+        <v>-0.06002849239478496</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
         <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.05114512595092206</v>
+        <v>0.03357826794251404</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.1696128908421519</v>
+        <v>0.007917610223412447</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0007680187180275119</v>
+        <v>0.03307405446379076</v>
       </c>
       <c r="EK3" t="n">
         <v>-0</v>
@@ -1994,82 +1994,82 @@
         <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.01488807133827899</v>
+        <v>0.01603766907909312</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.1200554313553673</v>
+        <v>-0.0044718750409675</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.1163305792293154</v>
+        <v>0.06597451278612271</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
         <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.07658033848008881</v>
+        <v>0.05011469107937589</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.06821098946899877</v>
+        <v>-0.03011420660587465</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.05581180389665538</v>
+        <v>0.03269277894455711</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.03892471088471504</v>
+        <v>0.1272729650443225</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.03594295406760953</v>
+        <v>0.004127938416997705</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.05851171741160065</v>
+        <v>0.005012902207539478</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
         <v>-0</v>
@@ -2081,22 +2081,22 @@
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0.03693467357498469</v>
+        <v>0.09873478300090864</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.001997422260029773</v>
+        <v>0.001011597945861453</v>
       </c>
       <c r="FS3" t="n">
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.008062355307563548</v>
+        <v>0.004837926208107368</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
         <v>0</v>
@@ -2108,16 +2108,16 @@
         <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.008854709098835414</v>
+        <v>0.091223641522495</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0.0268428890902545</v>
+        <v>0.01558429793877122</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
@@ -2129,27 +2129,27 @@
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1157060764438912</v>
+        <v>0.07705187086216993</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-4.381003496508733e-11</v>
+        <v>-4.017980780249189e-11</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.02154324716420207</v>
+        <v>-0.01621856073603004</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,22 +2161,22 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01988232608596831</v>
+        <v>0.0192932714179716</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07453232535269566</v>
+        <v>0.0789017933124409</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005117623896205646</v>
+        <v>0.002751471750652592</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2188,85 +2188,85 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1092963731830016</v>
+        <v>0.02860069902080098</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01808359687965713</v>
+        <v>-0.0194996850394848</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05657733834082453</v>
+        <v>-0.01056487557734647</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.004727153634901054</v>
+        <v>-0.01269855311997258</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0005346832724111117</v>
+        <v>-0.01696330382379465</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.0008590238141589076</v>
+        <v>-0.02774854972816288</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03834080843543736</v>
+        <v>0.0733684617414835</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.05225442176188559</v>
+        <v>-0.0225319188666454</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.00668061094539626</v>
+        <v>0.02822140492821378</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,25 +2275,25 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.311438614299604</v>
+        <v>0.1969077219222134</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.01007503999554014</v>
+        <v>-0.04708694555357935</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1798338169119971</v>
+        <v>-0.07335427097469088</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
         <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
@@ -2302,16 +2302,16 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.002789825596383139</v>
+        <v>-0.005408008412002227</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.01592097500776283</v>
+        <v>-0.003668767673136016</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.01113303092260914</v>
+        <v>-0.003156450700872838</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,31 +2320,31 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.008318309960835456</v>
+        <v>-0.007346576153070382</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.08861552920100668</v>
+        <v>0.02123447293853654</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.01511598894591164</v>
+        <v>0.04915042724370479</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,43 +2356,43 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1696349403159557</v>
+        <v>0.1195482766601019</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.008569042223938447</v>
+        <v>-0.03237977885177147</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.02561438009382859</v>
+        <v>-0.001021127961943646</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.06164390646963726</v>
+        <v>-0.07246359555319425</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.006255633320510558</v>
+        <v>0.05007224320578599</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.01001280497821044</v>
+        <v>0.009277124862864989</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
@@ -2404,82 +2404,82 @@
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.02352227211466479</v>
+        <v>-0.04663131645700852</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.07556595302617036</v>
+        <v>0.06802512478653269</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.152103886422063</v>
+        <v>0.03547401519219909</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.05197049331167936</v>
+        <v>-0.07439234331547698</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.03170402467527488</v>
+        <v>0.05707721469398794</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.00690645028025879</v>
+        <v>0.0105390545761526</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.06263395450229321</v>
+        <v>-0.0313182505009133</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.0009595381594896473</v>
+        <v>-0.004338867982509473</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.0005240110449673685</v>
+        <v>0.0008057603840706834</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2491,25 +2491,25 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.07957912045134345</v>
+        <v>-0.03938694620191682</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.06766927515359145</v>
+        <v>0.01054015833594557</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.01555695967402018</v>
+        <v>-0.03516055770171911</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,52 +2518,52 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.04975847941182061</v>
+        <v>0.02822627332211678</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.04175380707472436</v>
+        <v>0.03891460157883754</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.0331517896674432</v>
+        <v>-0.01563766298576637</v>
       </c>
       <c r="EB4" t="n">
         <v>-0</v>
       </c>
       <c r="EC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED4" t="n">
         <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.02875058241945795</v>
+        <v>-0.05360763915019531</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.02857166471424529</v>
+        <v>0.04371766889987315</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.0126054114278456</v>
+        <v>0.02134106997521628</v>
       </c>
       <c r="EK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
@@ -2572,103 +2572,103 @@
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.01606252263536143</v>
+        <v>-0.04397366017440711</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.009926897662246862</v>
+        <v>-0.04467884778197697</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.03952847557281514</v>
+        <v>0.005986615480916255</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW4" t="n">
         <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.05472476859839176</v>
+        <v>-0.08127441694294793</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.01436580676728745</v>
+        <v>0.0536426549998206</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.02260693341974461</v>
+        <v>0.004709344585264532</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.003372630787946866</v>
+        <v>-0.02984169119331556</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.0273989084258209</v>
+        <v>0.01226434578629864</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0162480076648586</v>
+        <v>-0.00438839198866211</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN4" t="n">
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0002639623743089583</v>
+        <v>0.001743392391271987</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.02658246960512216</v>
+        <v>0.06700442610036184</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0001972188459564776</v>
+        <v>-0.0006324510026345518</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW4" t="n">
         <v>0</v>
@@ -2677,31 +2677,31 @@
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01345154033418694</v>
+        <v>-0.0608488592385345</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.02774370510365376</v>
+        <v>0.02752535662366113</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01808107841530356</v>
+        <v>0.1861405696942631</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02075253694227735</v>
+        <v>0.0648228156257241</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01070367275032399</v>
+        <v>-0.06433072434723631</v>
       </c>
       <c r="G5" t="n">
         <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,34 +2736,34 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00212023390644215</v>
+        <v>0.07581945814552876</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.004740745219582553</v>
+        <v>0.002625401326100069</v>
       </c>
       <c r="O5" t="n">
-        <v>0.007165007315722827</v>
+        <v>0.04720450081769043</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.004392142965576806</v>
+        <v>0.1178981325986712</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2772,16 +2772,16 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01664938734451722</v>
+        <v>-0.1048137728701116</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01450437238320628</v>
+        <v>0.01557612764133034</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>-0</v>
@@ -2790,34 +2790,34 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.006195336165972003</v>
+        <v>-0.02343156084709627</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.004599583552354823</v>
+        <v>-0.08842988492118509</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.005047858325624885</v>
+        <v>-0.007417252527338424</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.008150099697762505</v>
+        <v>0.1230095231327265</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,67 +2826,67 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01417778955592969</v>
+        <v>0.07438549972323301</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.005077769289869142</v>
+        <v>-0.08092876231360555</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.04005098814174397</v>
+        <v>0.4102192396766714</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.04163993346619745</v>
+        <v>-0.13203106732142</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.01408306301089056</v>
+        <v>-0.1654308109607302</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.003806849883540182</v>
+        <v>0.001619438540323752</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.003949904551189053</v>
+        <v>-0.001085668671235475</v>
       </c>
       <c r="BH5" t="n">
-        <v>-6.870451662413168e-12</v>
+        <v>-3.825788645214988e-11</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,28 +2895,28 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.02906409005323345</v>
+        <v>0.004525582232391389</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.009139890534434696</v>
+        <v>0.07863687481268437</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.007820293317936629</v>
+        <v>0.1155764717650175</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.01581883701473324</v>
+        <v>0.3118639568915221</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,13 +2934,13 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.01685546329645605</v>
+        <v>-0.003378102906077582</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.006140347032504503</v>
+        <v>-0.07862704761253227</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
@@ -2952,7 +2952,7 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.001397117522862069</v>
+        <v>-0.1267045119222948</v>
       </c>
       <c r="CF5" t="n">
         <v>-0</v>
@@ -2961,10 +2961,10 @@
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01110329992139854</v>
+        <v>-0.07665564661471967</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01246334177225603</v>
+        <v>0.09031213990905053</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
@@ -2976,52 +2976,52 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.004953814733111788</v>
+        <v>-0.1136164868214565</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.005794119067710096</v>
+        <v>0.07516371333869508</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.00311782304142607</v>
+        <v>0.03962878538499055</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.004329380393796219</v>
+        <v>-0.1059686588136999</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01141049303760553</v>
+        <v>-0.07479982509642732</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0173547145041173</v>
+        <v>0.09095241449787611</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3033,52 +3033,52 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.01014965950866239</v>
+        <v>-0.04400665954185926</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01493441694104632</v>
+        <v>-0.06980215664822632</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.001081091137580629</v>
+        <v>0.01850431245016634</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.007650229630019773</v>
+        <v>-0.1000133088880532</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01466405336299622</v>
+        <v>0.0008886722208896135</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.01170284569256172</v>
+        <v>0.00443139365763412</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,19 +3087,19 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.01652982034700215</v>
+        <v>0.04442815269053535</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.01748361699316266</v>
+        <v>-0.01924285623993234</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.006969706185586012</v>
+        <v>0.111501239801644</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
@@ -3114,34 +3114,34 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.001668841511381553</v>
+        <v>-0.01748945396729461</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.004188509385504927</v>
+        <v>-0.1169659686137053</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01354103574320805</v>
+        <v>-0.006657724791671332</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.01124590422212374</v>
+        <v>-0.06235087907432847</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,25 +3150,25 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02343539993126122</v>
+        <v>-0.177088837181964</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.01169029768731737</v>
+        <v>0.1045092146435275</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.006693344343733003</v>
+        <v>-0.1282910229648296</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,25 +3177,25 @@
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01124518710053034</v>
+        <v>-0.09342153116680865</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.01480650359275847</v>
+        <v>0.07115946237426515</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.01691890513627431</v>
+        <v>-0.08522027870692159</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
@@ -3204,25 +3204,25 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.0262930069552429</v>
+        <v>0.01796331689670634</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01299193849661571</v>
+        <v>0.07554921702337618</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.001838791789290084</v>
+        <v>0.02514615373961926</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
@@ -3231,25 +3231,25 @@
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0002580190248027499</v>
+        <v>0.005113733383246244</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.01615090926342004</v>
+        <v>-0.07287248572889829</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.01356575339606802</v>
+        <v>-0.04759639394827264</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0005317746204269919</v>
+        <v>0.04583532983535034</v>
       </c>
       <c r="GE5" t="n">
         <v>0</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.968943528725536</v>
+        <v>0.135655230585964</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1970574861923935</v>
+        <v>-0.04361462908748355</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06157547767304161</v>
+        <v>-0.01935855355169244</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,25 +3868,25 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3879436511521692</v>
+        <v>0.09554377057797167</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08353235558251411</v>
+        <v>0.02725615838668089</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.09356939009209425</v>
+        <v>-0.01653471571376771</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7" t="n">
         <v>-0</v>
@@ -3898,55 +3898,55 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2479952849814566</v>
+        <v>0.03269234620726032</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2515578293617153</v>
+        <v>-0.02879380190357346</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1758844493728873</v>
+        <v>-0.02926602648446512</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1617411645519984</v>
+        <v>-0.01052105436909872</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.07096569028182363</v>
+        <v>-0.03048822733943517</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.03722359860434137</v>
+        <v>-0.03800137273727064</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -3955,22 +3955,22 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.2255453983137462</v>
+        <v>0.08366037165709457</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1516820580159356</v>
+        <v>-0.03144013206756224</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.1546229348461195</v>
+        <v>0.03610723197964299</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3982,43 +3982,43 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.691498095115758</v>
+        <v>0.2297840278453643</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.1514154140557345</v>
+        <v>-0.08309336945635462</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.4337596849734446</v>
+        <v>-0.09501941115097332</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
         <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.09371026023515665</v>
+        <v>-0.01150267022325527</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.02682889496529975</v>
+        <v>-0.0111052548907651</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.15099753897451</v>
+        <v>-0.008916385855339328</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,31 +4027,31 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.2337679578767394</v>
+        <v>-0.003894434758575448</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.3777933065925229</v>
+        <v>0.02074942961009765</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1633554037297867</v>
+        <v>0.06193214180986273</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,19 +4063,19 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.7328767324136317</v>
+        <v>0.143072119343383</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.04835485754702243</v>
+        <v>-0.02256377615601471</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.07342114476682336</v>
+        <v>-0.01689008789505255</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
@@ -4090,46 +4090,46 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.3619883446006504</v>
+        <v>-0.0829352656161251</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.07522367759875485</v>
+        <v>0.06168077628893878</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.1037282413417378</v>
+        <v>0.008382425240285096</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.04473780268224482</v>
+        <v>-0.05161568085489168</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.3206228622708786</v>
+        <v>0.08218750450412332</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.3074664455633244</v>
+        <v>0.04036267351534996</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,52 +4138,52 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.2644873817797008</v>
+        <v>-0.08680902290925788</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.2031366300633432</v>
+        <v>0.06919795087325228</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.09377621329094495</v>
+        <v>0.01650019076382933</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.141874092582798</v>
+        <v>-0.02452010618120686</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.04696887494759353</v>
+        <v>-0.005903265533278529</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01792222222788148</v>
+        <v>-0.008520417772753083</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4198,19 +4198,19 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.1523688542612331</v>
+        <v>-0.05478105795843822</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.1122223913620181</v>
+        <v>0.02547949893232686</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.0557331232404992</v>
+        <v>-0.0371633132489532</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,22 +4225,22 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.01106479321707968</v>
+        <v>0.01510490543763979</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.1208815325199325</v>
+        <v>0.03284247619597554</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.2624697512382388</v>
+        <v>-0.01743241715824331</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
         <v>0</v>
@@ -4252,49 +4252,49 @@
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1634441557251635</v>
+        <v>-0.05460083852060841</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.05984740518787142</v>
+        <v>0.05962797790007555</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.005723065521913749</v>
+        <v>0.01399105301790874</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.2670337665994224</v>
+        <v>-0.05071779971496675</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.2517397490030591</v>
+        <v>-0.03321891646215611</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.211781571067022</v>
+        <v>0.0004272358058173959</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,46 +4306,46 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.2931882491933997</v>
+        <v>-0.09427895295586035</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.1381637523841</v>
+        <v>0.06566381479435217</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.1147280810624108</v>
+        <v>0.00615203050662965</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.1070011609854826</v>
+        <v>-0.04924337478708585</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.1698466447098732</v>
+        <v>0.02313349149377464</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.1019406359954347</v>
+        <v>0.01173345223824619</v>
       </c>
       <c r="FL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
@@ -4354,61 +4354,61 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.0805258482745691</v>
+        <v>0.005172594800001169</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.2888288169247817</v>
+        <v>0.1054864757308326</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.2059642270862633</v>
+        <v>-0.01459989477539552</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.1535928198012563</v>
+        <v>-0.06233955743917512</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.1225856817144016</v>
+        <v>0.01674381962152145</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4985,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.07409809841155242</v>
+        <v>0.1920559598613019</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,16 +4994,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.001010501144959636</v>
+        <v>0.02111262581476532</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0188245679322062</v>
+        <v>-0.06712358487127801</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02361258438372476</v>
+        <v>0.1866207304460027</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,25 +5021,25 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.01373533512411179</v>
+        <v>-0.01152831122090504</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01486182731091898</v>
+        <v>0.03580104087517397</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0003782832630641333</v>
+        <v>0.06146965956461824</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -5048,37 +5048,37 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01550690881174723</v>
+        <v>-0.05570411938338765</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01720979942702628</v>
+        <v>0.02672263619065254</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01355442924802779</v>
+        <v>-0.02004644674717681</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01520958321514903</v>
+        <v>-0.06931337646655968</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.002553107500805654</v>
+        <v>0.008757730166703118</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -5087,13 +5087,13 @@
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01571222954998852</v>
+        <v>0.09736919566383781</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -5102,79 +5102,79 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.01367973981812708</v>
+        <v>0.02621437225459757</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.02095623774972656</v>
+        <v>-0.07489490155031986</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1206579920009236</v>
+        <v>0.4062882040792202</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.02321129565762126</v>
+        <v>-0.0846469779995638</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.01128055675983488</v>
+        <v>-0.149793315288492</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
         <v>-0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01026112768660947</v>
+        <v>-0.02827300387552399</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.01295588603744178</v>
+        <v>-0.0409981653260706</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.004073762316605502</v>
+        <v>-0.009474964146053914</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.04086940369408578</v>
+        <v>0.01384966574356533</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,16 +5183,16 @@
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.02949502977866195</v>
+        <v>0.1014485536121232</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01177060490231275</v>
+        <v>0.09020965695172264</v>
       </c>
       <c r="BR9" t="n">
         <v>-0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT9" t="n">
         <v>0</v>
@@ -5201,25 +5201,25 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.04072588145962502</v>
+        <v>0.2352565868927655</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.01914927426553633</v>
+        <v>0.006699450414198188</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.02668714159782738</v>
+        <v>-0.05449215399398342</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
         <v>-0</v>
@@ -5228,130 +5228,130 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.01184913963622457</v>
+        <v>-0.09039544073141931</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.005764813448715134</v>
+        <v>-0.009072328282105675</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01756495576417817</v>
+        <v>0.06457791308275447</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.01498449868007981</v>
+        <v>-0.06681877528509908</v>
       </c>
       <c r="CO9" t="n">
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.00307432315568105</v>
+        <v>0.14299805641508</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.03614038568698184</v>
+        <v>-0.009314300009635876</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.00544222139215826</v>
+        <v>-0.08220722835036968</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.004632567809716727</v>
+        <v>0.007927067532682937</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.02220311843645416</v>
+        <v>0.07264278467162306</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.006343783207812185</v>
+        <v>-0.03895437156310252</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02235743706732342</v>
+        <v>-0.06396692565415048</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01723152392337644</v>
+        <v>0.1101311962024065</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.004903670455946701</v>
+        <v>-0.07059926482347538</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.02318123436990634</v>
+        <v>-0.002866203476041111</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.009767034600952912</v>
+        <v>0.03992290794428824</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,25 +5363,25 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.03114134946756604</v>
+        <v>-0.01979349245105629</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.04204995294597248</v>
+        <v>-0.1052962833031925</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.01261231293142093</v>
+        <v>0.02192024749051551</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,76 +5390,76 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.00147894435260471</v>
+        <v>-0.01647376480410893</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.01418207772024053</v>
+        <v>-0.03753087774654863</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.003549460159730025</v>
+        <v>-0.008386219591984292</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.007304610128145383</v>
+        <v>-0.0430230032307863</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.02253884199606523</v>
+        <v>-0.1541079613066094</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.06751952384848119</v>
+        <v>-0.156868008554034</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-1.856226689747918e-05</v>
+        <v>-0.09498244584769318</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.005983243191846322</v>
+        <v>-0.01574741211603953</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.02243345896983556</v>
+        <v>0.05274451048180866</v>
       </c>
       <c r="FD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
@@ -5471,64 +5471,64 @@
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02550202577918903</v>
+        <v>-0.1063498555068317</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.04643909063345249</v>
+        <v>0.05231980461186866</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0.001999306572185119</v>
+        <v>0.03993250773744994</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.004196774776187968</v>
+        <v>0.0223368342249511</v>
       </c>
       <c r="FR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.01361575193949708</v>
+        <v>0.01391263065602984</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.04192889683166</v>
+        <v>-0.0868412366954681</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.02971755366777945</v>
+        <v>-0.03130233352435158</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
@@ -5537,13 +5537,13 @@
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.009805020150686369</v>
+        <v>-0.01881099812288553</v>
       </c>
       <c r="GE9" t="n">
         <v>0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.317401890929302</v>
+        <v>0.2090108161243885</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.07550971439595072</v>
+        <v>-0.06340058596384858</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0705996235276546</v>
+        <v>-0.04776432079842852</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5575,25 +5575,25 @@
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1822178799622051</v>
+        <v>0.169025227225057</v>
       </c>
       <c r="L10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.005472043199097058</v>
+        <v>-0.007342814288480838</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.07011793590326452</v>
+        <v>-0.05594348953739991</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
@@ -5602,85 +5602,85 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.08160327242972101</v>
+        <v>0.05356168337708497</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.01201215096621219</v>
+        <v>-0.03710352144686071</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01841419191950702</v>
+        <v>-0.0350197957609405</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.03592745647174608</v>
+        <v>-0.01255382219998254</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.02920278324119504</v>
+        <v>-0.02080636077090521</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.01750750095850584</v>
+        <v>-0.06403252166378197</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.06542078983042168</v>
+        <v>0.1030101598569635</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.05593994721855851</v>
+        <v>-0.03510689168325787</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.05208507806049505</v>
+        <v>0.03882653119287932</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,16 +5689,16 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.4599096308987309</v>
+        <v>0.284631744244496</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.04358382426704074</v>
+        <v>-0.100285880487866</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1601922537787962</v>
+        <v>-0.1373534381398155</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,7 +5707,7 @@
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0200134832502852</v>
+        <v>-0.0235574323493514</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.02303452127710965</v>
+        <v>-0.002767042304610316</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.09762790188377224</v>
+        <v>-0.02302221889990824</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,22 +5743,22 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.06180006381827693</v>
+        <v>0.006110425771579723</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.1102161429432142</v>
+        <v>0.0408846964218644</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.06391518302849176</v>
+        <v>0.06238393522252116</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,25 +5770,25 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.2149896239879942</v>
+        <v>0.186000093720418</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.01738366115700804</v>
+        <v>-0.07826169465150834</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.00581109909297237</v>
+        <v>-0.02606874776410549</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
@@ -5797,46 +5797,46 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.0853766779866766</v>
+        <v>-0.09667714261210826</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.02547798866801731</v>
+        <v>0.08330733555857384</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.01172017705829459</v>
+        <v>0.01087591769518715</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.01659754368909416</v>
+        <v>-0.07086477635221285</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.08210127161521875</v>
+        <v>0.09027736545650347</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.1548936097206099</v>
+        <v>0.04522958318509815</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
@@ -5845,55 +5845,55 @@
         <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.06922340153879666</v>
+        <v>-0.0993106721043899</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.05609324909501885</v>
+        <v>0.09209861473897973</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.00767471841180587</v>
+        <v>0.02003684482726874</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.06662622147709875</v>
+        <v>-0.0739198800734943</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.04942591537303195</v>
+        <v>0.06488101011939057</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.008614699933207307</v>
+        <v>-0.03942852232935684</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5905,19 +5905,19 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.057321014623948</v>
+        <v>-0.05235898776810592</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.0498189098628652</v>
+        <v>0.01854029982034962</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.02311826314052172</v>
+        <v>-0.05139899422666361</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
@@ -5932,127 +5932,127 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.05671093710186327</v>
+        <v>0.03892365983757264</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.03324703202621691</v>
+        <v>0.0433827625336741</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.02670571293515658</v>
+        <v>-0.03643244406790214</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.04533369962983966</v>
+        <v>-0.04953323719882727</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.08499345631903028</v>
+        <v>0.0777440318156454</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0394178201867043</v>
+        <v>0.01123260233724682</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.07458140693346803</v>
+        <v>-0.05928454099201546</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0.08690052848052233</v>
+        <v>-0.07576717173655666</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.03150735439692439</v>
+        <v>-0.008822862489180891</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.08198283592064363</v>
+        <v>-0.1123162169168733</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.04623528162730747</v>
+        <v>0.09137207328794282</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.02624237935308806</v>
+        <v>0.004824095945113462</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.02432624161312803</v>
+        <v>-0.05248761269701889</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.06982953904711922</v>
+        <v>0.0370312125562721</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.007719333924433118</v>
+        <v>0.01000852420342824</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
@@ -6061,25 +6061,25 @@
         <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.01228361496928154</v>
+        <v>0.01512901684490796</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.01038944490045009</v>
+        <v>0.1012148962786196</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.04459213049625744</v>
+        <v>-0.01776760212504224</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
@@ -6091,31 +6091,31 @@
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.01227418138279028</v>
+        <v>-0.06347262847801524</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.01043845579397489</v>
+        <v>0.02289633217197167</v>
       </c>
       <c r="GC10" t="n">
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6689,46 +6689,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2405250633790278</v>
+        <v>0.07368745841086563</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.01099388952997482</v>
+        <v>-0.00794148239820989</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.02540422139248317</v>
+        <v>-0.02118595058552093</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1180824945735405</v>
+        <v>0.06969138412309377</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01593671114098565</v>
+        <v>0.01293471461914588</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.02992651017097423</v>
+        <v>-0.02565841124407583</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6743,22 +6743,22 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04502183588129569</v>
+        <v>0.02368178297910406</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01632902226940804</v>
+        <v>-0.004025578180014187</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03779737479518474</v>
+        <v>-0.001578845001368259</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6767,49 +6767,49 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03183170208521436</v>
+        <v>-0.008509116668804004</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.003052564242493552</v>
+        <v>-0.02367986846683786</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.004261808995115875</v>
+        <v>-0.02522039501375737</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.008994886870062765</v>
+        <v>0.03769092787495879</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.02108118889582042</v>
+        <v>-0.004679016736998861</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.03606297760286489</v>
+        <v>0.03145806408597124</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6818,52 +6818,52 @@
         <v>-0</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT12" t="n">
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3099358299993245</v>
+        <v>0.1155341669333288</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.03371357328690709</v>
+        <v>-0.004852877403496188</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.08296854667319818</v>
+        <v>-0.05542413850817959</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
         <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03722446170227364</v>
+        <v>-0.02253934479320903</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.03322695860758582</v>
+        <v>-0.006205990442460746</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.03952931446428998</v>
+        <v>-0.008375725736306005</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,19 +6881,19 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.09477747912820794</v>
+        <v>0.02102767318648595</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0198045025690955</v>
+        <v>0.01750313812980208</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.111283457966407</v>
+        <v>0.04626394304699707</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
@@ -6908,25 +6908,25 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1256368771419532</v>
+        <v>0.08295064026952545</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.02403481543805705</v>
+        <v>-0.0227810736854646</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.02841119567792526</v>
+        <v>-0.004493595329311096</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>-0</v>
@@ -6935,49 +6935,49 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.06294531271545256</v>
+        <v>-0.03060620556517329</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0005882962978957572</v>
+        <v>0.02708497218241333</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.00462882724930595</v>
+        <v>0.0149721392144205</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.05441114436852572</v>
+        <v>-0.04078945775209139</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.04516299872830268</v>
+        <v>0.03233862487584787</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.06309756598718837</v>
+        <v>0.02069119610122563</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,19 +6986,19 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.04592411434849162</v>
+        <v>-0.02947256138186391</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.01023694110346573</v>
+        <v>0.02991695771346448</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.00366175165077739</v>
+        <v>0.01616565965643995</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7007,7 +7007,7 @@
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
@@ -7016,73 +7016,73 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.01189369783781799</v>
+        <v>-0.0003147202443800678</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.05338789724743435</v>
+        <v>0.006031245836712409</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.003473025211826404</v>
+        <v>-0.00467779791092504</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.07484772587364941</v>
+        <v>-0.02812887524272134</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.005956239477943573</v>
+        <v>-0.01601798473489447</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.01240386892092468</v>
+        <v>-0.0147691454659052</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.008165109358129861</v>
+        <v>0.03137813506773284</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.002876604475511319</v>
+        <v>0.01696093855692828</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.02306088081742628</v>
+        <v>-0.04472255760104775</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>0</v>
@@ -7091,22 +7091,22 @@
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.04169407482531069</v>
+        <v>0.00491605733557121</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.006391493591573521</v>
+        <v>0.02540821213366689</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.03457628557852842</v>
+        <v>0.0271939080346324</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
@@ -7115,7 +7115,7 @@
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,25 +7124,25 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.03528274081756448</v>
+        <v>-0.0235437349061687</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.006746463771513366</v>
+        <v>0.02888565795953601</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02137782751605978</v>
+        <v>-0.001212387507587524</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
@@ -7151,16 +7151,16 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.04480431402936478</v>
+        <v>-0.03485539073952303</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.00408399201523011</v>
+        <v>0.03634709013158966</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.009102785108378142</v>
+        <v>0.008644422610093117</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7169,61 +7169,61 @@
         <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.006760059286966606</v>
+        <v>-0.001796465116390063</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.008750210145990178</v>
+        <v>-0.004998836336297333</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.03057380478933131</v>
+        <v>-0.01640866385209265</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.0344209362701104</v>
+        <v>0.01097835393682549</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.0185281628740137</v>
+        <v>0.03253710023928285</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01200319399258214</v>
+        <v>-0.04160612019418968</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
@@ -7232,19 +7232,19 @@
         <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.01164688439981328</v>
+        <v>-0.01039663594247801</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.02353956260837786</v>
+        <v>-0.002470280471085319</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,22 +7261,22 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2135057995205869</v>
+        <v>0.1941846983960328</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01237776698536058</v>
+        <v>-0.01795608856864285</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1315757678595164</v>
+        <v>-0.06942799823377811</v>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>-0</v>
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1415004828764477</v>
+        <v>0.2419201690677768</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,16 +7297,16 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0006642386351963899</v>
+        <v>-0.05593874027460137</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.08578575147507045</v>
+        <v>-0.03797995098267383</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,46 +7315,46 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.007228649095991116</v>
+        <v>0.0497100593748569</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0326160221711702</v>
+        <v>-0.04481590314195141</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.01172996269236593</v>
+        <v>-0.008112333244984773</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0240168190447089</v>
+        <v>-0.01780136947630516</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0159165254892629</v>
+        <v>-0.05879604096479292</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.008100572267075258</v>
+        <v>-0.006967289906052285</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,13 +7363,13 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01439375666295845</v>
+        <v>0.04834665957522494</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.02608569606168486</v>
+        <v>0.01744092919651516</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.05682130556794465</v>
+        <v>-0.02995728562400564</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1985679563719102</v>
+        <v>0.2646920865351556</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.01503205416187031</v>
+        <v>-0.09223372144374233</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.09414995745155283</v>
+        <v>-0.05677418832892109</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
@@ -7423,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0649187886604595</v>
+        <v>-0.01152842078488327</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,64 +7432,64 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.0166935279638781</v>
+        <v>-0.04606841284654022</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.04392668615204108</v>
+        <v>-0.02929384247331759</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0794129911090815</v>
+        <v>0.01347142210183761</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.04498586784939468</v>
+        <v>0.04691375630580286</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.008748146686882525</v>
+        <v>-0.004645842058890267</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.08257811660822328</v>
+        <v>0.15782074980308</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.02190775250500923</v>
+        <v>-0.0259518863509191</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.01476069823580125</v>
+        <v>-0.03666398367321498</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7504,73 +7504,73 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.04993886497280662</v>
+        <v>-0.08604736191199421</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01201107760543597</v>
+        <v>0.007447563402470351</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.04095378623099811</v>
+        <v>0.04415029157028771</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.02886231808541092</v>
+        <v>-0.1089133399388062</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.03066438324440131</v>
+        <v>0.08525710390946993</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.03956435674915799</v>
+        <v>0.0617511008603146</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.03362785587319484</v>
+        <v>-0.08044722974863686</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.01106139215777083</v>
+        <v>-0.0004039441204592564</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.03938899289545613</v>
+        <v>0.04540500938779275</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7585,22 +7585,22 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.008921215687593638</v>
+        <v>-0.01037054467868846</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.002342889346380009</v>
+        <v>-0.02535936628205941</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.002748003748301864</v>
+        <v>0.0171372825189276</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>-0</v>
@@ -7612,46 +7612,46 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.03481373779601962</v>
+        <v>-0.03962628797698566</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01761608684704431</v>
+        <v>0.001636899106810825</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.01694227974620748</v>
+        <v>-0.01838688659229808</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.01109121634508808</v>
+        <v>0.05297120904806499</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.02201584362307029</v>
+        <v>0.007649300019184685</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.003726581763730272</v>
+        <v>-0.06792821837644089</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
@@ -7660,13 +7660,13 @@
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
         <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.02357448414094813</v>
+        <v>-0.008839311943119064</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,37 +7675,37 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.005794144862769945</v>
+        <v>-0.02679084790361788</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.02929157263353591</v>
+        <v>0.01941938199840366</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.03392949415934619</v>
+        <v>-0.01762478249032255</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.0172283107327352</v>
+        <v>-0.05310952941832105</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.06760550551288035</v>
+        <v>0.04581505559296407</v>
       </c>
       <c r="EU13" t="n">
         <v>-0</v>
@@ -7714,40 +7714,40 @@
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.03698533064773213</v>
+        <v>-0.09090575090193631</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.004102814909191448</v>
+        <v>-0.01043205652409473</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.04329570694112581</v>
+        <v>0.03863607283418668</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.007562205553510219</v>
+        <v>-0.08162650601516185</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,67 +7756,67 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.0241030616933597</v>
+        <v>0.0497092119516512</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.02187571869888806</v>
+        <v>0.03545277299008946</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.02066674835346598</v>
+        <v>0.04333847621721909</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.02919942467142914</v>
+        <v>-0.02376979457481788</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.002386297375134996</v>
+        <v>-0.0007823210013507438</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.0257237289553458</v>
+        <v>-0.01994598622823264</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.02574806309782275</v>
+        <v>-0.005030325051620247</v>
       </c>
       <c r="GE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF13" t="n">
         <v>-0</v>
@@ -7833,13 +7833,13 @@
         <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.2519206278128838</v>
+        <v>-0.1977381383672376</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4644133203339205</v>
+        <v>0.1357875355235617</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1016241398580506</v>
+        <v>-0.1649379231835754</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7848,7 +7848,7 @@
         <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
         <v>-0</v>
@@ -7860,67 +7860,67 @@
         <v>-0</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1745571250404921</v>
+        <v>-0.1391681741187606</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4359963771231085</v>
+        <v>0.08168944380103772</v>
       </c>
       <c r="N14" t="n">
-        <v>0.07841882100629083</v>
+        <v>-0.1124612768406479</v>
       </c>
       <c r="O14" t="n">
         <v>-0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R14" t="n">
         <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
         <v>-0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.09245490910434274</v>
+        <v>-0.06781754628971405</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1084704459195704</v>
+        <v>0.1390431501196886</v>
       </c>
       <c r="W14" t="n">
-        <v>0.02723134249279414</v>
+        <v>0.06156071415310299</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
         <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.007737854295346812</v>
+        <v>-0.02256170143467364</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.06302217443790752</v>
+        <v>-0.125396204504337</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.07427757282908536</v>
+        <v>-0.1610852190873372</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
@@ -7935,46 +7935,46 @@
         <v>-0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.01615452050987275</v>
+        <v>-0.1308577580437343</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.03731767991452688</v>
+        <v>0.1401787315703043</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.08474922907447602</v>
+        <v>0.001753396101202453</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.2524138251309161</v>
+        <v>-0.3699263469075003</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.3668346403851201</v>
+        <v>0.4598085640446797</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.2056764185976775</v>
+        <v>-0.3300420009281796</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -7995,13 +7995,13 @@
         <v>-0</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.03425842458276317</v>
+        <v>0.05121901420099146</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.04868358396573294</v>
+        <v>-0.3544844192420861</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.0663891059641674</v>
+        <v>-0.133880285855678</v>
       </c>
       <c r="BH14" t="n">
         <v>-0</v>
@@ -8010,52 +8010,52 @@
         <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>-0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.06828435189620728</v>
+        <v>0.07023433082007693</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0.01584060468758893</v>
+        <v>0.1369759040484146</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.2280470408332326</v>
+        <v>0.2235742733870872</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0.175956622537477</v>
+        <v>-0.2293685291303476</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.211139633108347</v>
+        <v>0.4557456721570197</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.1382220604318974</v>
+        <v>-0.0367017696872496</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -8064,55 +8064,55 @@
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0979422981427621</v>
+        <v>0.1204741364423746</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.1184953471436963</v>
+        <v>-0.03008123263117408</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.00238970668555553</v>
+        <v>0.04513692960612966</v>
       </c>
       <c r="CI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.01401306682935665</v>
+        <v>0.05884882445215767</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.04901473448808686</v>
+        <v>0.04061656623600618</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.1545908702281278</v>
+        <v>0.222320317334193</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
@@ -8121,31 +8121,31 @@
         <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
         <v>-0</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.06674203692169811</v>
+        <v>0.09509873054442911</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.1092906601949527</v>
+        <v>-0.03256072119164621</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.02135537857614709</v>
+        <v>0.0798664415517836</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
         <v>-0</v>
@@ -8154,43 +8154,43 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG14" t="n">
-        <v>-0.002270358570333797</v>
+        <v>0.05952471114318505</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.1302928784509849</v>
+        <v>-0.0854308001558856</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.01530457836228684</v>
+        <v>-0.01119621743588281</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO14" t="n">
         <v>0</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.07719079371652487</v>
+        <v>-0.003186140188232605</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0.06087896741775049</v>
+        <v>-0.08678002849746062</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.1538998241291619</v>
+        <v>0.222830100015488</v>
       </c>
       <c r="DS14" t="n">
         <v>-0</v>
@@ -8199,58 +8199,58 @@
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>-0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX14" t="n">
         <v>-0</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.01797694216079114</v>
+        <v>-0.07858067367396343</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.06342064093045059</v>
+        <v>-0.08930261928859538</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.05708943152078913</v>
+        <v>-0.06520147254209063</v>
       </c>
       <c r="EB14" t="n">
         <v>-0</v>
       </c>
       <c r="EC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE14" t="n">
         <v>0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.1109191059134638</v>
+        <v>0.02444593065278483</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.1609339806552007</v>
+        <v>0.02251482729885302</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.07134121912560196</v>
+        <v>-0.05849575417571433</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
@@ -8259,52 +8259,52 @@
         <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.06003894422382937</v>
+        <v>-0.011595672813429</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.08424938302656507</v>
+        <v>-0.04500428734041936</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.0112129264215429</v>
+        <v>0.005899655474594132</v>
       </c>
       <c r="ET14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV14" t="n">
         <v>-0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.08808058639559699</v>
+        <v>0.1011003420542533</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.1171133432268986</v>
+        <v>-0.07321518100872111</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.02482949144978528</v>
+        <v>0.04925043104597729</v>
       </c>
       <c r="FC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
         <v>-0</v>
@@ -8316,82 +8316,82 @@
         <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.03719681939620881</v>
+        <v>0.176032884291757</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0641661079777783</v>
+        <v>-0.1080367787874539</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.09629759880656921</v>
+        <v>-0.1368106174646108</v>
       </c>
       <c r="FL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.01151946397541326</v>
+        <v>-0.002434835592242997</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.004077981931311757</v>
+        <v>0.01796561485085727</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.01551990419886814</v>
+        <v>0.2289467514311956</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY14" t="n">
         <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.02538230419058228</v>
+        <v>0.0931844005648685</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.03466164184984804</v>
+        <v>-0.1145058069272267</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
         <v>0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -8965,25 +8965,25 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1566437264370825</v>
+        <v>0.2854196834686287</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1175366762424607</v>
+        <v>0.02127201765781847</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.04514935816704488</v>
+        <v>-0.119452022227292</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
         <v>-0</v>
@@ -8992,25 +8992,25 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1009211092596984</v>
+        <v>0.3694728569015375</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1114723964734888</v>
+        <v>-0.04309779759059834</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.04669117786075598</v>
+        <v>-0.1189553185409733</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -9019,10 +9019,10 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.02733032660640064</v>
+        <v>0.09789200654394827</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
@@ -9031,40 +9031,40 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.002203030867498847</v>
+        <v>-0.07293757301143879</v>
       </c>
       <c r="X16" t="n">
-        <v>0.04352926171195127</v>
+        <v>0.008476743764068605</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0261003669833195</v>
+        <v>-0.03895011306489732</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.01770614656781483</v>
+        <v>-0.1605844481559862</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.01883148804045089</v>
+        <v>-0.02817373013357484</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>-0</v>
@@ -9073,25 +9073,25 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.03212034106725826</v>
+        <v>0.06605390945613869</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.01674407455039825</v>
+        <v>-0.007980491385033829</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.01237747126980075</v>
+        <v>-0.04374609423385774</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
@@ -9100,10 +9100,10 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.1508884672652813</v>
+        <v>0.4230371496629063</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -9112,16 +9112,16 @@
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.05479863519513084</v>
+        <v>-0.1603075897059981</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.01567937648752562</v>
+        <v>-0.08250136828367378</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
@@ -9130,61 +9130,61 @@
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.03936241610540049</v>
+        <v>-0.04121598693372197</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.07161565649268493</v>
+        <v>-0.06670982417417533</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.02915761414087213</v>
+        <v>-0.04745418685138157</v>
       </c>
       <c r="BI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.06740911988584357</v>
+        <v>0.06496027276765466</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.03467603473504213</v>
+        <v>0.07836526801134741</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.02913422197453842</v>
+        <v>0.02393014507096757</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.07085385074898513</v>
+        <v>0.2438410183924441</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
@@ -9193,40 +9193,40 @@
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.01824554229193541</v>
+        <v>-0.03130085726003111</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.02245034208230704</v>
+        <v>-0.07931232650539173</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
         <v>-0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.0252156295637642</v>
+        <v>-0.1031416470235996</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.01807144646155812</v>
+        <v>0.004497718238138855</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.01909336737462082</v>
+        <v>0.05743200343634688</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
@@ -9238,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.02014366620588855</v>
+        <v>-0.1909656873819032</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,10 +9247,10 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.01261294147731497</v>
+        <v>0.1559879045463095</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.01512206953770835</v>
+        <v>0.04027768206909457</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
@@ -9262,28 +9262,28 @@
         <v>0</v>
       </c>
       <c r="CV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.01487484835880896</v>
+        <v>-0.09220518576614571</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.01686386231302077</v>
+        <v>-0.01819858290507267</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.02320425746844368</v>
+        <v>0.0624824330853411</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
         <v>0</v>
@@ -9292,52 +9292,52 @@
         <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.03181835035882476</v>
+        <v>-0.06651740289773142</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.01567097418517957</v>
+        <v>-0.09193398922627234</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.002149173990826084</v>
+        <v>-0.01471418724648844</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
         <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.02249835513820455</v>
+        <v>-0.05072881738368108</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.01566551894752598</v>
+        <v>-0.01810522084347314</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.04541454402276354</v>
+        <v>0.005433820057526554</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
         <v>-0</v>
@@ -9346,7 +9346,7 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.001509793550464594</v>
+        <v>0.04085338904406585</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
@@ -9355,40 +9355,40 @@
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.04657647424601626</v>
+        <v>0.01684021999944549</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0.03918974260778076</v>
+        <v>0.04338103353360318</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
         <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.01100639709529513</v>
+        <v>-0.01502656623793315</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI16" t="n">
         <v>0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.01636545521202453</v>
+        <v>-0.04376055315184023</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.006839335476701154</v>
+        <v>0.03753317492787178</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
@@ -9397,55 +9397,55 @@
         <v>-0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.01258486439836308</v>
+        <v>-0.01567618961743605</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.003418295557571784</v>
+        <v>-0.09712124793104755</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.02849241277330387</v>
+        <v>0.05788769486825215</v>
       </c>
       <c r="EU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.01197143519795206</v>
+        <v>-0.1161239555826585</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.01534501636328289</v>
+        <v>-0.01571718768363444</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.02724323841535088</v>
+        <v>0.0450844029713891</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF16" t="n">
         <v>-0</v>
@@ -9454,61 +9454,61 @@
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.02132477803415763</v>
+        <v>-0.1103913960227252</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.03688646658851693</v>
+        <v>0.1003408296529179</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.02271458307663037</v>
+        <v>0.02934449167803166</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.003773498455755642</v>
+        <v>0.0129384338293536</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS16" t="n">
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.004224424193985276</v>
+        <v>-0.01486295665988928</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.004050662723730501</v>
+        <v>0.003834574319552106</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.0306456047135306</v>
+        <v>-0.06132816419568109</v>
       </c>
       <c r="GA16" t="n">
         <v>0</v>
@@ -9517,16 +9517,16 @@
         <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.0269794285513892</v>
+        <v>0.04587010290466945</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
         <v>0</v>
@@ -9537,22 +9537,22 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.533327109661073</v>
+        <v>0.6868942711573436</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2056590042442166</v>
+        <v>-0.3213586716245641</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1109241751068049</v>
+        <v>-0.06248519146528263</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
         <v>-0</v>
@@ -9564,22 +9564,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4180086253428794</v>
+        <v>0.6622907742398613</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2050396185250667</v>
+        <v>-0.3507088288998083</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1372093146748894</v>
+        <v>-0.1377989732297713</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -9588,52 +9588,52 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1303575123407011</v>
+        <v>0.1605759335669958</v>
       </c>
       <c r="U17" t="n">
         <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01944030959570561</v>
+        <v>-0.08138992101301355</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0979719518751896</v>
+        <v>-0.0991118931287556</v>
       </c>
       <c r="X17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1638235332077469</v>
+        <v>-0.1322267556743601</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.01092584729030333</v>
+        <v>-0.1805067020511942</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.02700088152868859</v>
+        <v>-0.1810240566782473</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>-0</v>
@@ -9645,22 +9645,22 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.05240423202752784</v>
+        <v>0.2258400398082659</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.03964756752178086</v>
+        <v>-0.1257779529138318</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.0271483089462283</v>
+        <v>0.1016560953265927</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9669,28 +9669,28 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.4667595910890149</v>
+        <v>0.5827639664238856</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.01699609068802892</v>
+        <v>-0.1414704105943547</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.1463324694655206</v>
+        <v>-0.2817644953786412</v>
       </c>
       <c r="AY17" t="n">
         <v>-0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>-0</v>
@@ -9699,16 +9699,16 @@
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.04299433442375855</v>
+        <v>0.003328072470685241</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.08864583927519402</v>
+        <v>-0.1066592994579326</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.2308453265277348</v>
+        <v>-0.08866978300894073</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
@@ -9717,7 +9717,7 @@
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -9726,22 +9726,22 @@
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.06104914191070304</v>
+        <v>-0.05528870286600171</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.06430292397972964</v>
+        <v>-0.001371399386634887</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.0583940788600456</v>
+        <v>0.09894174622913422</v>
       </c>
       <c r="BQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
@@ -9753,25 +9753,25 @@
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.2365293984561278</v>
+        <v>0.4496590890122489</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0.008126002287173823</v>
+        <v>-0.1894718874421979</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.09244830419894441</v>
+        <v>-0.05665401987693289</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
@@ -9780,22 +9780,22 @@
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.1149340349068447</v>
+        <v>-0.227078156907467</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.02241199098586386</v>
+        <v>0.1899312803654196</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.025283091435917</v>
+        <v>0.01538099043062824</v>
       </c>
       <c r="CI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
@@ -9807,19 +9807,19 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.04820295019759652</v>
+        <v>-0.2796215681867803</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.115444593253792</v>
+        <v>0.419351090674231</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.1737778301437115</v>
+        <v>0.1946232398168982</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
@@ -9834,22 +9834,22 @@
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.09674009010893674</v>
+        <v>-0.2040170534450156</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.03699827110942987</v>
+        <v>0.1936462599775425</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.02656632519853875</v>
+        <v>0.03079289245682469</v>
       </c>
       <c r="DA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>-0</v>
@@ -9861,22 +9861,22 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.0787515952246422</v>
+        <v>-0.199368077485802</v>
       </c>
       <c r="DG17" t="n">
         <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.0192538371394742</v>
+        <v>0.03818445775604369</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.02404489221159057</v>
+        <v>-0.1301584328048495</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL17" t="n">
         <v>0</v>
@@ -9888,16 +9888,16 @@
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.05852781457454773</v>
+        <v>-0.1242684283160456</v>
       </c>
       <c r="DP17" t="n">
         <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0.04493538528909904</v>
+        <v>0.1048579901030299</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.09945938949279699</v>
+        <v>0.01766558306264052</v>
       </c>
       <c r="DS17" t="n">
         <v>-0</v>
@@ -9912,25 +9912,25 @@
         <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.05146309075236124</v>
+        <v>0.04887642568712147</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0.02916565457368673</v>
+        <v>-0.09122730675737672</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.02592346448004339</v>
+        <v>0.05929441916220687</v>
       </c>
       <c r="EB17" t="n">
         <v>0</v>
       </c>
       <c r="EC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED17" t="n">
         <v>0</v>
@@ -9939,52 +9939,52 @@
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.05758726612818021</v>
+        <v>-0.1705452756858847</v>
       </c>
       <c r="EH17" t="n">
         <v>0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.04537154329243431</v>
+        <v>0.1141887812570186</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.06317766908223829</v>
+        <v>0.06814224814484439</v>
       </c>
       <c r="EK17" t="n">
         <v>-0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
         <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.09319660550793883</v>
+        <v>-0.1213647259659694</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.01788806520437384</v>
+        <v>0.1026713404522997</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.04534142220156908</v>
+        <v>-0.05571717253871085</v>
       </c>
       <c r="ET17" t="n">
         <v>-0</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
@@ -9993,25 +9993,25 @@
         <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.1082874879391497</v>
+        <v>-0.2466939999194325</v>
       </c>
       <c r="EZ17" t="n">
         <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.04616956768202974</v>
+        <v>0.2095659465988268</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.02631460797304026</v>
+        <v>0.004850073975817645</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
@@ -10023,19 +10023,19 @@
         <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.01287162411875933</v>
+        <v>-0.1549517362859618</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.08228907473608459</v>
+        <v>0.1248598863948395</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.06318979636045685</v>
+        <v>0.03572360308828611</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
@@ -10044,69 +10044,69 @@
         <v>0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
         <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.004949982858417232</v>
+        <v>0.005664916335099371</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.0390581862523651</v>
+        <v>0.07594238877948455</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.02097379652329779</v>
+        <v>-0.01974199075733479</v>
       </c>
       <c r="FU17" t="n">
         <v>-0</v>
       </c>
       <c r="FV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW17" t="n">
         <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.02112527654752658</v>
+        <v>-0.2283025324328295</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.07246067092718492</v>
+        <v>0.08434732110958575</v>
       </c>
       <c r="GC17" t="n">
         <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.8661138350864519</v>
+        <v>-0.4163555713697962</v>
       </c>
       <c r="C18" t="n">
         <v>-0</v>
@@ -10115,13 +10115,13 @@
         <v>-0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1056010534398206</v>
+        <v>0.06491735788041866</v>
       </c>
       <c r="F18" t="n">
-        <v>1.381581778664646</v>
+        <v>0.3328506322715526</v>
       </c>
       <c r="G18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10133,7 +10133,7 @@
         <v>-0</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8378239580026087</v>
+        <v>-0.5343515724815189</v>
       </c>
       <c r="L18" t="n">
         <v>-0</v>
@@ -10142,10 +10142,10 @@
         <v>-0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.07926753307328696</v>
+        <v>0.2037909867398973</v>
       </c>
       <c r="O18" t="n">
-        <v>1.08327224425393</v>
+        <v>0.2727870781275356</v>
       </c>
       <c r="P18" t="n">
         <v>-0</v>
@@ -10157,25 +10157,25 @@
         <v>-0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.07570462224822232</v>
+        <v>-0.09659026642840282</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V18" t="n">
         <v>-0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0937742920839798</v>
+        <v>0.09991958117487153</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1017209648535416</v>
+        <v>0.01849751313791912</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -10184,22 +10184,22 @@
         <v>-0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.09824545058723289</v>
+        <v>-0.05084479388028042</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.06936064161970702</v>
+        <v>0.2298378407876982</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.1070022834113431</v>
+        <v>0.08303699542728951</v>
       </c>
       <c r="AH18" t="n">
         <v>-0</v>
@@ -10214,22 +10214,22 @@
         <v>-0</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.09421067907301922</v>
+        <v>-0.1230653880816601</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN18" t="n">
         <v>-0</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.0307278068534118</v>
+        <v>-0.06595239568980624</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.2570643225861307</v>
+        <v>0.1052756877660499</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -10238,37 +10238,37 @@
         <v>-0</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU18" t="n">
-        <v>-0.8706133299938622</v>
+        <v>-0.6606555293139199</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW18" t="n">
         <v>-0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.2856269341205661</v>
+        <v>0.1623287261669639</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.8945139052046281</v>
+        <v>0.2481148125376448</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD18" t="n">
-        <v>-0.3816973857410147</v>
+        <v>0.03386493480062957</v>
       </c>
       <c r="BE18" t="n">
         <v>-0</v>
@@ -10277,10 +10277,10 @@
         <v>-0</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.09191288483727596</v>
+        <v>0.1478743455988389</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.3281482554585992</v>
+        <v>0.09512908993367744</v>
       </c>
       <c r="BI18" t="n">
         <v>-0</v>
@@ -10289,28 +10289,28 @@
         <v>0</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM18" t="n">
-        <v>-0.3375819099535404</v>
+        <v>-0.01813169710373446</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>-0.2029767895585202</v>
+        <v>-0.09036699957976703</v>
       </c>
       <c r="BQ18" t="n">
-        <v>-0.02798786573744131</v>
+        <v>0.04317995508757226</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS18" t="n">
         <v>-0</v>
@@ -10322,19 +10322,19 @@
         <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>-0.2902363668031562</v>
+        <v>-0.2606648338345511</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
         <v>-0</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.04831583555840343</v>
+        <v>0.06674778709065794</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.3880980178111461</v>
+        <v>0.1506725515687527</v>
       </c>
       <c r="CA18" t="n">
         <v>0</v>
@@ -10349,49 +10349,49 @@
         <v>0</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.2273993229124811</v>
+        <v>0.1920470572425541</v>
       </c>
       <c r="CF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG18" t="n">
         <v>0</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.01245901486126814</v>
+        <v>-0.02347760502745163</v>
       </c>
       <c r="CI18" t="n">
-        <v>-0.2469672859915561</v>
+        <v>-0.1023339727392493</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK18" t="n">
         <v>-0</v>
       </c>
       <c r="CL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM18" t="n">
         <v>-0</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.1494445924223441</v>
+        <v>0.2568357702751184</v>
       </c>
       <c r="CO18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.2191122633074467</v>
+        <v>-0.2200732823764084</v>
       </c>
       <c r="CR18" t="n">
-        <v>0.1487131461372993</v>
+        <v>-0.1607391373342727</v>
       </c>
       <c r="CS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT18" t="n">
         <v>0</v>
@@ -10400,25 +10400,25 @@
         <v>0</v>
       </c>
       <c r="CV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW18" t="n">
-        <v>0.1661004441834657</v>
+        <v>0.1785180092530771</v>
       </c>
       <c r="CX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY18" t="n">
         <v>-0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.02333982641576177</v>
+        <v>-0.02372373756526226</v>
       </c>
       <c r="DA18" t="n">
-        <v>-0.21414845392995</v>
+        <v>-0.1112175811132124</v>
       </c>
       <c r="DB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC18" t="n">
         <v>0</v>
@@ -10430,46 +10430,46 @@
         <v>-0</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.1965170928173414</v>
+        <v>0.09176232263317025</v>
       </c>
       <c r="DG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH18" t="n">
         <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.2320503379960899</v>
+        <v>0.1877302654572076</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.00659680952005076</v>
+        <v>-0.06428573749910341</v>
       </c>
       <c r="DK18" t="n">
         <v>-0</v>
       </c>
       <c r="DL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.115341861088489</v>
+        <v>0.07277111887311032</v>
       </c>
       <c r="DP18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.131161354694727</v>
+        <v>0.008383927157542059</v>
       </c>
       <c r="DS18" t="n">
-        <v>-0.06705169866223634</v>
+        <v>0.02592709001644895</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.06137192022364975</v>
+        <v>-0.009445920057172714</v>
       </c>
       <c r="DY18" t="n">
         <v>0</v>
@@ -10493,10 +10493,10 @@
         <v>0</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.09210550661453289</v>
+        <v>-0.0799190505488815</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.0693730837453678</v>
+        <v>0.08301085667827464</v>
       </c>
       <c r="EC18" t="n">
         <v>0</v>
@@ -10505,25 +10505,25 @@
         <v>-0</v>
       </c>
       <c r="EE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF18" t="n">
         <v>0</v>
       </c>
       <c r="EG18" t="n">
-        <v>0.1577043059883702</v>
+        <v>0.09284477733791295</v>
       </c>
       <c r="EH18" t="n">
         <v>-0</v>
       </c>
       <c r="EI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>-0.1159879443444339</v>
+        <v>0.01189689830465382</v>
       </c>
       <c r="EK18" t="n">
-        <v>-0.1998383270343046</v>
+        <v>-0.02299438416870891</v>
       </c>
       <c r="EL18" t="n">
         <v>-0</v>
@@ -10532,25 +10532,25 @@
         <v>0</v>
       </c>
       <c r="EN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.03921553674121378</v>
+        <v>0.10912653161011</v>
       </c>
       <c r="EQ18" t="n">
         <v>0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>-0.1191824465682167</v>
+        <v>0.07203414727621736</v>
       </c>
       <c r="ET18" t="n">
-        <v>-0.07062829067712698</v>
+        <v>-0.1451584052198678</v>
       </c>
       <c r="EU18" t="n">
         <v>0</v>
@@ -10559,13 +10559,13 @@
         <v>-0</v>
       </c>
       <c r="EW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX18" t="n">
         <v>0</v>
       </c>
       <c r="EY18" t="n">
-        <v>0.1591754144519025</v>
+        <v>0.2174561069944374</v>
       </c>
       <c r="EZ18" t="n">
         <v>0</v>
@@ -10574,13 +10574,13 @@
         <v>0</v>
       </c>
       <c r="FB18" t="n">
-        <v>-0.07215831824496409</v>
+        <v>-0.001148348750593392</v>
       </c>
       <c r="FC18" t="n">
-        <v>-0.2353511219417157</v>
+        <v>-0.1094897856519592</v>
       </c>
       <c r="FD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE18" t="n">
         <v>-0</v>
@@ -10592,34 +10592,34 @@
         <v>-0</v>
       </c>
       <c r="FH18" t="n">
-        <v>0.09825463319488811</v>
+        <v>0.2176954110443302</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
         <v>0</v>
       </c>
       <c r="FK18" t="n">
-        <v>-0.00233365482107545</v>
+        <v>-0.1229710679387403</v>
       </c>
       <c r="FL18" t="n">
-        <v>-0.2344832213983266</v>
+        <v>-0.1048960242726675</v>
       </c>
       <c r="FM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.0006420093904002752</v>
+        <v>-0.003514653164907911</v>
       </c>
       <c r="FR18" t="n">
         <v>0</v>
@@ -10628,25 +10628,25 @@
         <v>0</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.01038923732864633</v>
+        <v>0.008219148118817837</v>
       </c>
       <c r="FU18" t="n">
-        <v>-0.2003696079792475</v>
+        <v>-0.04707034454482698</v>
       </c>
       <c r="FV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX18" t="n">
         <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.06085055908048532</v>
+        <v>0.0957465113748799</v>
       </c>
       <c r="GA18" t="n">
         <v>-0</v>
@@ -10655,10 +10655,10 @@
         <v>0</v>
       </c>
       <c r="GC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD18" t="n">
-        <v>0.2277728241723411</v>
+        <v>-0.009559260379833099</v>
       </c>
       <c r="GE18" t="n">
         <v>0</v>
@@ -10672,10 +10672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.9627810858716969</v>
+        <v>-0.4427284690323877</v>
       </c>
       <c r="C19" t="n">
         <v>-0</v>
@@ -10684,10 +10684,10 @@
         <v>-0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5580713317651814</v>
+        <v>-0.001187218368029678</v>
       </c>
       <c r="F19" t="n">
-        <v>1.298183167867996</v>
+        <v>0.3740227888063745</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -10699,10 +10699,10 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.065577023464297</v>
+        <v>-0.6501697471536243</v>
       </c>
       <c r="L19" t="n">
         <v>-0</v>
@@ -10711,13 +10711,13 @@
         <v>-0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2306222070952266</v>
+        <v>0.1595914262140453</v>
       </c>
       <c r="O19" t="n">
-        <v>1.022970653929317</v>
+        <v>0.2924724281031678</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -10729,22 +10729,22 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1313222433411778</v>
+        <v>-0.1249925286424892</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V19" t="n">
         <v>-0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1165816659835937</v>
+        <v>0.08594598112030075</v>
       </c>
       <c r="X19" t="n">
-        <v>0.08367694090214239</v>
+        <v>0.009493644431816021</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -10756,19 +10756,19 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.2515242342061572</v>
+        <v>-0.04380399269839386</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>-0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.01665510242003584</v>
+        <v>0.2465655634371144</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.1659589408580795</v>
+        <v>0.1105352393565443</v>
       </c>
       <c r="AH19" t="n">
         <v>-0</v>
@@ -10780,25 +10780,25 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.2441292892456852</v>
+        <v>-0.1271742132488865</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.06320441540668546</v>
+        <v>-0.0408796763892857</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.2340998838323554</v>
+        <v>0.1446813482314282</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -10807,37 +10807,37 @@
         <v>-0</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU19" t="n">
-        <v>-0.7946637456438979</v>
+        <v>-0.7737148635689268</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW19" t="n">
         <v>-0</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.4306956920134923</v>
+        <v>0.1541239905976612</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.8834035981960774</v>
+        <v>0.1906333700604987</v>
       </c>
       <c r="AZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD19" t="n">
-        <v>-0.2171745553458702</v>
+        <v>0.03059150650604054</v>
       </c>
       <c r="BE19" t="n">
         <v>-0</v>
@@ -10846,40 +10846,40 @@
         <v>-0</v>
       </c>
       <c r="BG19" t="n">
-        <v>0.3863426418846669</v>
+        <v>0.1245638700509836</v>
       </c>
       <c r="BH19" t="n">
-        <v>0.2168382356882357</v>
+        <v>0.1621479883664657</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ19" t="n">
         <v>0</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM19" t="n">
-        <v>-0.06296567691961599</v>
+        <v>-0.1279519485839473</v>
       </c>
       <c r="BN19" t="n">
         <v>0</v>
       </c>
       <c r="BO19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.07873084786801655</v>
+        <v>-0.1252873315531066</v>
       </c>
       <c r="BQ19" t="n">
-        <v>-0.06761981494951227</v>
+        <v>-0.06174001176630795</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS19" t="n">
         <v>-0</v>
@@ -10891,7 +10891,7 @@
         <v>0</v>
       </c>
       <c r="BV19" t="n">
-        <v>-0.4964234448227871</v>
+        <v>-0.4810358975330622</v>
       </c>
       <c r="BW19" t="n">
         <v>-0</v>
@@ -10900,25 +10900,25 @@
         <v>-0</v>
       </c>
       <c r="BY19" t="n">
-        <v>0.1354722237437793</v>
+        <v>0.03691799465358063</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0.4020563904837512</v>
+        <v>0.1228875827679576</v>
       </c>
       <c r="CA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB19" t="n">
         <v>0</v>
       </c>
       <c r="CC19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE19" t="n">
-        <v>0.2627801695989425</v>
+        <v>0.1844611151732015</v>
       </c>
       <c r="CF19" t="n">
         <v>0</v>
@@ -10927,13 +10927,13 @@
         <v>0</v>
       </c>
       <c r="CH19" t="n">
-        <v>-0.075095156636362</v>
+        <v>-0.03041870622136355</v>
       </c>
       <c r="CI19" t="n">
-        <v>-0.2601940686459377</v>
+        <v>-0.1187809698893082</v>
       </c>
       <c r="CJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK19" t="n">
         <v>-0</v>
@@ -10945,19 +10945,19 @@
         <v>-0</v>
       </c>
       <c r="CN19" t="n">
-        <v>0.1081172129949199</v>
+        <v>0.3813818967910489</v>
       </c>
       <c r="CO19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP19" t="n">
         <v>0</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.2624348470135766</v>
+        <v>-0.1644849792217718</v>
       </c>
       <c r="CR19" t="n">
-        <v>0.03665566968400303</v>
+        <v>-0.1311773177629627</v>
       </c>
       <c r="CS19" t="n">
         <v>0</v>
@@ -10972,7 +10972,7 @@
         <v>0</v>
       </c>
       <c r="CW19" t="n">
-        <v>0.2190471015971596</v>
+        <v>0.1746429181725196</v>
       </c>
       <c r="CX19" t="n">
         <v>-0</v>
@@ -10981,10 +10981,10 @@
         <v>-0</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-0.06412452056992456</v>
+        <v>-0.003312136215994468</v>
       </c>
       <c r="DA19" t="n">
-        <v>-0.2876843701156171</v>
+        <v>-0.1186946843952984</v>
       </c>
       <c r="DB19" t="n">
         <v>-0</v>
@@ -10999,19 +10999,19 @@
         <v>-0</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.1582406885783395</v>
+        <v>0.08662046160016373</v>
       </c>
       <c r="DG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH19" t="n">
         <v>0</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0.1349932725530059</v>
+        <v>0.06453278664852842</v>
       </c>
       <c r="DJ19" t="n">
-        <v>-0.06148743941833405</v>
+        <v>-0.01181858403113432</v>
       </c>
       <c r="DK19" t="n">
         <v>-0</v>
@@ -11020,31 +11020,31 @@
         <v>-0</v>
       </c>
       <c r="DM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO19" t="n">
-        <v>0.02903574685996979</v>
+        <v>0.03501222540876811</v>
       </c>
       <c r="DP19" t="n">
         <v>0</v>
       </c>
       <c r="DQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR19" t="n">
-        <v>0.03492213034347456</v>
+        <v>0.05336576512493955</v>
       </c>
       <c r="DS19" t="n">
-        <v>-0.2090554416885022</v>
+        <v>-0.08906304272378403</v>
       </c>
       <c r="DT19" t="n">
         <v>0</v>
       </c>
       <c r="DU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV19" t="n">
         <v>0</v>
@@ -11053,46 +11053,46 @@
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>-0.1034023934243307</v>
+        <v>-0.03502305127321514</v>
       </c>
       <c r="DY19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ19" t="n">
         <v>-0</v>
       </c>
       <c r="EA19" t="n">
-        <v>0.153364322670606</v>
+        <v>0.06765074152926084</v>
       </c>
       <c r="EB19" t="n">
-        <v>-0.08923112873353908</v>
+        <v>-0.01358905844111879</v>
       </c>
       <c r="EC19" t="n">
         <v>0</v>
       </c>
       <c r="ED19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG19" t="n">
-        <v>0.228544352597338</v>
+        <v>0.04921113559576266</v>
       </c>
       <c r="EH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ19" t="n">
-        <v>-0.1643459861479985</v>
+        <v>0.04737819712843377</v>
       </c>
       <c r="EK19" t="n">
-        <v>-0.198754582309558</v>
+        <v>-0.05308571172849836</v>
       </c>
       <c r="EL19" t="n">
         <v>0</v>
@@ -11101,40 +11101,40 @@
         <v>0</v>
       </c>
       <c r="EN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP19" t="n">
-        <v>0.2066488841493347</v>
+        <v>0.1175879174766288</v>
       </c>
       <c r="EQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES19" t="n">
-        <v>-0.06261683204164721</v>
+        <v>0.05399372662603898</v>
       </c>
       <c r="ET19" t="n">
-        <v>0.04060706664041137</v>
+        <v>0.09496362077430683</v>
       </c>
       <c r="EU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY19" t="n">
-        <v>0.2463037825251546</v>
+        <v>0.198642005771973</v>
       </c>
       <c r="EZ19" t="n">
         <v>0</v>
@@ -11143,13 +11143,13 @@
         <v>0</v>
       </c>
       <c r="FB19" t="n">
-        <v>-0.07960400970659036</v>
+        <v>0.004817484628512505</v>
       </c>
       <c r="FC19" t="n">
-        <v>-0.2838912445986057</v>
+        <v>-0.09628890710427999</v>
       </c>
       <c r="FD19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE19" t="n">
         <v>-0</v>
@@ -11158,22 +11158,22 @@
         <v>0</v>
       </c>
       <c r="FG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH19" t="n">
-        <v>0.09119283903488529</v>
+        <v>0.2082423011262997</v>
       </c>
       <c r="FI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ19" t="n">
         <v>0</v>
       </c>
       <c r="FK19" t="n">
-        <v>0.02139559330771896</v>
+        <v>-0.08057859143497705</v>
       </c>
       <c r="FL19" t="n">
-        <v>-0.1842970475420644</v>
+        <v>-0.05535981401020114</v>
       </c>
       <c r="FM19" t="n">
         <v>-0</v>
@@ -11182,25 +11182,25 @@
         <v>-0</v>
       </c>
       <c r="FO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>0.08947185146314408</v>
+        <v>0.3316351401591671</v>
       </c>
       <c r="FR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS19" t="n">
         <v>0</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.4729365362906646</v>
+        <v>-0.01248988637487609</v>
       </c>
       <c r="FU19" t="n">
-        <v>-0.2598126526732241</v>
+        <v>0.01121807519353148</v>
       </c>
       <c r="FV19" t="n">
         <v>0</v>
@@ -11212,31 +11212,31 @@
         <v>-0</v>
       </c>
       <c r="FY19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>0.105574876402189</v>
+        <v>0.1040728634530788</v>
       </c>
       <c r="GA19" t="n">
         <v>-0</v>
       </c>
       <c r="GB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC19" t="n">
         <v>-0</v>
       </c>
       <c r="GD19" t="n">
-        <v>0.1466112530903053</v>
+        <v>0.05888673965104309</v>
       </c>
       <c r="GE19" t="n">
         <v>0</v>
       </c>
       <c r="GF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="20">
@@ -11244,19 +11244,19 @@
         <v>-0</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.07074334259496176</v>
+        <v>-0.1615146191496996</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.08971421453755714</v>
+        <v>-0.05804152529741116</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01654249920726381</v>
+        <v>0.07226993950212447</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5955594831927888</v>
+        <v>0.3405837659509504</v>
       </c>
       <c r="G20" t="n">
         <v>-0</v>
@@ -11268,22 +11268,22 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.09404922667153187</v>
+        <v>-0.2063210143643892</v>
       </c>
       <c r="L20" t="n">
         <v>-0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.04980512802234512</v>
+        <v>-0.04922660925568057</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0339316794886177</v>
+        <v>0.301461419340587</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5036954182231775</v>
+        <v>0.3479148070087125</v>
       </c>
       <c r="P20" t="n">
         <v>-0</v>
@@ -11295,25 +11295,25 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.06271430173925228</v>
+        <v>-0.08896544813507164</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.001000808147758416</v>
+        <v>0.0404245109074109</v>
       </c>
       <c r="W20" t="n">
-        <v>0.07174015949698569</v>
+        <v>-0.03449092123427298</v>
       </c>
       <c r="X20" t="n">
-        <v>0.08852290216324252</v>
+        <v>0.05914733912256202</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -11322,28 +11322,28 @@
         <v>-0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.01617958423654121</v>
+        <v>0.01064455756261661</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.02547041340748316</v>
+        <v>0.08645443516855333</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.01040265496598124</v>
+        <v>0.003980567007195993</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.01264418799684098</v>
+        <v>0.03784324582746099</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
@@ -11352,79 +11352,79 @@
         <v>-0</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.01409712147893026</v>
+        <v>-0.08277099886843413</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>-0.0176389975634821</v>
+        <v>-0.06207252992305116</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.06801958936341691</v>
+        <v>-0.1699312057054881</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.06955850258677465</v>
+        <v>0.06438457220291469</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>-0.04279225477872495</v>
+        <v>-0.2589983191956225</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>-0.0482995509433963</v>
+        <v>-0.05405247255872038</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.06085643237306608</v>
+        <v>-0.1347584357475284</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.3357308414468869</v>
+        <v>0.3592319945819418</v>
       </c>
       <c r="AZ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
         <v>-0</v>
       </c>
       <c r="BD20" t="n">
-        <v>-0.06828890131449063</v>
+        <v>0.2103859339105316</v>
       </c>
       <c r="BE20" t="n">
         <v>-0</v>
       </c>
       <c r="BF20" t="n">
-        <v>-0.007021631823526012</v>
+        <v>0.08360073058345743</v>
       </c>
       <c r="BG20" t="n">
-        <v>0.05031055869257414</v>
+        <v>0.1541762836130085</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.1117448029749454</v>
+        <v>-0.01904087350021443</v>
       </c>
       <c r="BI20" t="n">
         <v>-0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK20" t="n">
         <v>0</v>
@@ -11433,25 +11433,25 @@
         <v>-0</v>
       </c>
       <c r="BM20" t="n">
-        <v>-0.06942826150253639</v>
+        <v>-0.01764747105800192</v>
       </c>
       <c r="BN20" t="n">
         <v>0</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.03432186029992509</v>
+        <v>0.008419622074454012</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.02240313905513296</v>
+        <v>-0.09326441602839074</v>
       </c>
       <c r="BQ20" t="n">
-        <v>-0.0153373549258293</v>
+        <v>-0.003376035002844907</v>
       </c>
       <c r="BR20" t="n">
         <v>0</v>
       </c>
       <c r="BS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT20" t="n">
         <v>-0</v>
@@ -11460,19 +11460,19 @@
         <v>-0</v>
       </c>
       <c r="BV20" t="n">
-        <v>-0.04132250613098955</v>
+        <v>-0.2010786304336254</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX20" t="n">
-        <v>0.0003891990218119908</v>
+        <v>-0.07564895432983693</v>
       </c>
       <c r="BY20" t="n">
-        <v>0.06067319776227491</v>
+        <v>-0.02371978998451297</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0.1631882168598484</v>
+        <v>0.2183814525903628</v>
       </c>
       <c r="CA20" t="n">
         <v>0</v>
@@ -11481,55 +11481,55 @@
         <v>0</v>
       </c>
       <c r="CC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE20" t="n">
-        <v>0.02129370980251248</v>
+        <v>0.1096833730144728</v>
       </c>
       <c r="CF20" t="n">
         <v>0</v>
       </c>
       <c r="CG20" t="n">
-        <v>0.02267553241342252</v>
+        <v>0.01581214368756033</v>
       </c>
       <c r="CH20" t="n">
-        <v>-0.01012819026342317</v>
+        <v>-0.01306860342040523</v>
       </c>
       <c r="CI20" t="n">
-        <v>-0.1097726674130544</v>
+        <v>-0.08615961094401721</v>
       </c>
       <c r="CJ20" t="n">
         <v>0</v>
       </c>
       <c r="CK20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL20" t="n">
         <v>-0</v>
       </c>
       <c r="CM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN20" t="n">
-        <v>0.009703316372177669</v>
+        <v>0.07652986150867287</v>
       </c>
       <c r="CO20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP20" t="n">
-        <v>-0.04772598009023676</v>
+        <v>-0.08269744149680767</v>
       </c>
       <c r="CQ20" t="n">
-        <v>-0.1383204951938403</v>
+        <v>-0.03595406769720064</v>
       </c>
       <c r="CR20" t="n">
-        <v>-0.01210677848109141</v>
+        <v>-0.1857493108669766</v>
       </c>
       <c r="CS20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT20" t="n">
         <v>0</v>
@@ -11538,76 +11538,76 @@
         <v>0</v>
       </c>
       <c r="CV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW20" t="n">
-        <v>0.001548145123435707</v>
+        <v>0.1185325187706849</v>
       </c>
       <c r="CX20" t="n">
         <v>-0</v>
       </c>
       <c r="CY20" t="n">
-        <v>0.02112716020515926</v>
+        <v>0.01114988291373544</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-0.004582810336981142</v>
+        <v>-0.05037811612934104</v>
       </c>
       <c r="DA20" t="n">
-        <v>-0.1133853001807561</v>
+        <v>-0.1043550588266941</v>
       </c>
       <c r="DB20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD20" t="n">
         <v>-0</v>
       </c>
       <c r="DE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF20" t="n">
-        <v>0.01870925856406306</v>
+        <v>0.05908186904415787</v>
       </c>
       <c r="DG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH20" t="n">
-        <v>-0.007569673156716238</v>
+        <v>-0.01652481086152815</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.003369237928202792</v>
+        <v>0.05489839456462114</v>
       </c>
       <c r="DJ20" t="n">
-        <v>-0.02934005261928483</v>
+        <v>-0.08281090518046332</v>
       </c>
       <c r="DK20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL20" t="n">
         <v>-0</v>
       </c>
       <c r="DM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO20" t="n">
-        <v>0.005149692329251689</v>
+        <v>0.01541066089938434</v>
       </c>
       <c r="DP20" t="n">
         <v>0</v>
       </c>
       <c r="DQ20" t="n">
-        <v>-0.02497424270509109</v>
+        <v>0.004851515884252913</v>
       </c>
       <c r="DR20" t="n">
-        <v>-0.02604216946854496</v>
+        <v>0.05410113244720774</v>
       </c>
       <c r="DS20" t="n">
-        <v>-0.03403144666180317</v>
+        <v>-0.04378966199842065</v>
       </c>
       <c r="DT20" t="n">
         <v>-0</v>
@@ -11622,46 +11622,46 @@
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>-0.01783888510335784</v>
+        <v>0.1548644243248079</v>
       </c>
       <c r="DY20" t="n">
         <v>0</v>
       </c>
       <c r="DZ20" t="n">
-        <v>0.02196596551527411</v>
+        <v>0.08783322836546931</v>
       </c>
       <c r="EA20" t="n">
-        <v>0.0452379860761315</v>
+        <v>0.03620913534805132</v>
       </c>
       <c r="EB20" t="n">
-        <v>0.1060290266870397</v>
+        <v>0.1067286564117487</v>
       </c>
       <c r="EC20" t="n">
         <v>0</v>
       </c>
       <c r="ED20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG20" t="n">
-        <v>-0.002828789881671709</v>
+        <v>0.141742243323438</v>
       </c>
       <c r="EH20" t="n">
         <v>0</v>
       </c>
       <c r="EI20" t="n">
-        <v>0.0566006568685551</v>
+        <v>-0.02716031279061266</v>
       </c>
       <c r="EJ20" t="n">
-        <v>-0.01988714889233464</v>
+        <v>-0.08944592192098746</v>
       </c>
       <c r="EK20" t="n">
-        <v>-0.08553709683882772</v>
+        <v>0.04228380602126118</v>
       </c>
       <c r="EL20" t="n">
         <v>0</v>
@@ -11670,28 +11670,28 @@
         <v>0</v>
       </c>
       <c r="EN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO20" t="n">
         <v>-0</v>
       </c>
       <c r="EP20" t="n">
-        <v>0.0140533740219218</v>
+        <v>-0.008211794815749778</v>
       </c>
       <c r="EQ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER20" t="n">
-        <v>0.0449850795844433</v>
+        <v>0.01829540983189423</v>
       </c>
       <c r="ES20" t="n">
-        <v>-0.003823480800546013</v>
+        <v>0.05559199580911818</v>
       </c>
       <c r="ET20" t="n">
-        <v>0.009163977628648769</v>
+        <v>-0.09327605844771038</v>
       </c>
       <c r="EU20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV20" t="n">
         <v>-0</v>
@@ -11700,82 +11700,82 @@
         <v>0</v>
       </c>
       <c r="EX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY20" t="n">
-        <v>0.002547673883844654</v>
+        <v>0.1456531264407579</v>
       </c>
       <c r="EZ20" t="n">
         <v>0</v>
       </c>
       <c r="FA20" t="n">
-        <v>0.02859490600419027</v>
+        <v>0.00218423619021791</v>
       </c>
       <c r="FB20" t="n">
-        <v>-0.03243960713292136</v>
+        <v>-0.01545085378655399</v>
       </c>
       <c r="FC20" t="n">
-        <v>-0.09999237689853438</v>
+        <v>-0.1105825454127447</v>
       </c>
       <c r="FD20" t="n">
         <v>0</v>
       </c>
       <c r="FE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF20" t="n">
         <v>0</v>
       </c>
       <c r="FG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH20" t="n">
-        <v>0.04852375545561106</v>
+        <v>0.03779516171485441</v>
       </c>
       <c r="FI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ20" t="n">
-        <v>0.02712319372163526</v>
+        <v>0.04650257256555826</v>
       </c>
       <c r="FK20" t="n">
-        <v>-0.06484732691083286</v>
+        <v>0.0315028017380128</v>
       </c>
       <c r="FL20" t="n">
-        <v>-0.05640769607458877</v>
+        <v>-0.04632639250314146</v>
       </c>
       <c r="FM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP20" t="n">
         <v>0</v>
       </c>
       <c r="FQ20" t="n">
-        <v>0.003984762870481025</v>
+        <v>0.1344477046283593</v>
       </c>
       <c r="FR20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS20" t="n">
-        <v>-0.01011276608073908</v>
+        <v>-0.2241891086216581</v>
       </c>
       <c r="FT20" t="n">
-        <v>-0.1563284591216802</v>
+        <v>-0.07865442390562555</v>
       </c>
       <c r="FU20" t="n">
-        <v>-0.03099230101908524</v>
+        <v>-0.05183679015332044</v>
       </c>
       <c r="FV20" t="n">
         <v>0</v>
       </c>
       <c r="FW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX20" t="n">
         <v>-0</v>
@@ -11784,22 +11784,22 @@
         <v>-0</v>
       </c>
       <c r="FZ20" t="n">
-        <v>0.007639415378545235</v>
+        <v>0.1169183687966906</v>
       </c>
       <c r="GA20" t="n">
         <v>-0</v>
       </c>
       <c r="GB20" t="n">
-        <v>0.03736327115060633</v>
+        <v>0.03105925015566889</v>
       </c>
       <c r="GC20" t="n">
         <v>-0</v>
       </c>
       <c r="GD20" t="n">
-        <v>0.05240565062675632</v>
+        <v>-0.01102014366802713</v>
       </c>
       <c r="GE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF20" t="n">
         <v>0</v>
